--- a/Result/profitability/6259.xlsx
+++ b/Result/profitability/6259.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15125</v>
+        <v>0.225</v>
       </c>
       <c r="N2" t="n">
-        <v>22.37125</v>
+        <v>22.40125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.17125</v>
+        <v>0.23375</v>
       </c>
       <c r="N3" t="n">
-        <v>21.75125</v>
+        <v>21.3675</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11625</v>
+        <v>0.155</v>
       </c>
       <c r="N4" t="n">
-        <v>21.44</v>
+        <v>21.30625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02124999999999998</v>
+        <v>0.10625</v>
       </c>
       <c r="N5" t="n">
-        <v>18.46375</v>
+        <v>18.15875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01624999999999999</v>
+        <v>0.06374999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>17.53375</v>
+        <v>17.395</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01875000000000002</v>
+        <v>0.02624999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>17.075</v>
+        <v>17.165</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02375000000000002</v>
+        <v>-0.001250000000000015</v>
       </c>
       <c r="N8" t="n">
-        <v>16.905</v>
+        <v>16.87875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04000000000000002</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>16.8075</v>
@@ -1772,7 +1772,7 @@
         <v>0.09</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.05125000000000002</v>
+        <v>-0.05125000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>16.8125</v>
@@ -2026,7 +2026,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07624999999999998</v>
+        <v>0.07625</v>
       </c>
       <c r="N13" t="n">
         <v>18.39</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>195</v>
+      </c>
+      <c r="D75" t="n">
+        <v>151</v>
+      </c>
+      <c r="E75" t="n">
+        <v>43</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.0875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4186046511627908</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2100000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.009362460989745913</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-9.714285714285714</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.440000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09894566098945667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
